--- a/research/traditional_assets/database/data/ireland/ireland_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_precious_metals.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.91</v>
+        <v>-1.158</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.154</v>
+        <v>1.619</v>
       </c>
       <c r="V2">
-        <v>0.06320422535211268</v>
+        <v>0.08512092534174553</v>
       </c>
       <c r="W2">
-        <v>-0.05108910891089109</v>
+        <v>-0.01127049180327869</v>
       </c>
       <c r="X2">
-        <v>0.06434381664798555</v>
+        <v>0.1225042463868321</v>
       </c>
       <c r="Y2">
-        <v>-0.1154329255588766</v>
+        <v>-0.1337747381901108</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.04926584234930449</v>
+        <v>-0.03852459016393443</v>
       </c>
       <c r="AB2">
-        <v>0.06323854204525853</v>
+        <v>0.1180667377260628</v>
       </c>
       <c r="AC2">
-        <v>-0.112697225644608</v>
+        <v>-0.1567279878463269</v>
       </c>
       <c r="AD2">
-        <v>0.8240000000000001</v>
+        <v>0.742</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.8240000000000001</v>
+        <v>0.742</v>
       </c>
       <c r="AG2">
-        <v>-1.33</v>
+        <v>-0.877</v>
       </c>
       <c r="AH2">
-        <v>0.02360760944304378</v>
+        <v>0.03754680700333974</v>
       </c>
       <c r="AI2">
-        <v>0.01726594585533485</v>
+        <v>0.01717513078098236</v>
       </c>
       <c r="AJ2">
-        <v>-0.04061068702290076</v>
+        <v>-0.04833820206140109</v>
       </c>
       <c r="AK2">
-        <v>-0.02918586789554531</v>
+        <v>-0.02109034942163865</v>
       </c>
       <c r="AL2">
-        <v>0.037</v>
+        <v>0.019</v>
       </c>
       <c r="AM2">
-        <v>0.037</v>
+        <v>0.019</v>
       </c>
       <c r="AN2">
-        <v>-0.526517571884984</v>
+        <v>-0.5010128291694801</v>
       </c>
       <c r="AO2">
-        <v>-58.70270270270271</v>
+        <v>-115.1052631578948</v>
       </c>
       <c r="AP2">
-        <v>0.8498402555910542</v>
+        <v>0.5921674544226875</v>
       </c>
       <c r="AQ2">
-        <v>-58.70270270270271</v>
+        <v>-115.1052631578948</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Conroy Gold and Natural Resources plc (AIM:CGNR)</t>
+          <t>Karelian Diamond Resources Plc (AIM:KDR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>0.258</v>
+        <v>0.015</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +722,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.85</v>
+        <v>0.127</v>
       </c>
       <c r="V3">
-        <v>0.1</v>
+        <v>0.06195121951219513</v>
       </c>
       <c r="W3">
-        <v>0.01316326530612245</v>
+        <v>0.001293103448275862</v>
       </c>
       <c r="X3">
-        <v>0.06434381664798555</v>
+        <v>0.1235146116677643</v>
       </c>
       <c r="Y3">
-        <v>-0.05118055134186311</v>
+        <v>-0.1222215082194884</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.04902912621359223</v>
+        <v>-0.03379416282642089</v>
       </c>
       <c r="AB3">
-        <v>0.06323854204525853</v>
+        <v>0.1180667377260628</v>
       </c>
       <c r="AC3">
-        <v>-0.1122676682588508</v>
+        <v>-0.1518609005524836</v>
       </c>
       <c r="AD3">
-        <v>0.63</v>
+        <v>0.179</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.63</v>
+        <v>0.179</v>
       </c>
       <c r="AG3">
-        <v>-1.22</v>
+        <v>0.05199999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.03293256664924203</v>
+        <v>0.08030506953790939</v>
       </c>
       <c r="AI3">
-        <v>0.02516979624450659</v>
+        <v>0.01724636284805858</v>
       </c>
       <c r="AJ3">
-        <v>-0.07060185185185186</v>
+        <v>0.0247383444338725</v>
       </c>
       <c r="AK3">
-        <v>-0.05263157894736843</v>
+        <v>0.005072181037846273</v>
       </c>
       <c r="AL3">
-        <v>0.024</v>
+        <v>0.008</v>
       </c>
       <c r="AM3">
-        <v>0.024</v>
-      </c>
-      <c r="AN3">
-        <v>-0.6237623762376238</v>
+        <v>0.008</v>
       </c>
       <c r="AO3">
-        <v>-42.08333333333334</v>
-      </c>
-      <c r="AP3">
-        <v>1.207920792079208</v>
+        <v>-49.5</v>
       </c>
       <c r="AQ3">
-        <v>-42.08333333333334</v>
+        <v>-49.5</v>
       </c>
     </row>
     <row r="4">
@@ -799,7 +793,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Karelian Diamond Resources Plc (AIM:KDR)</t>
+          <t>Conroy Gold and Natural Resources plc (AIM:CGNR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -808,7 +802,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-0.516</v>
+        <v>-0.275</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -832,67 +826,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.076</v>
+        <v>1.3</v>
       </c>
       <c r="V4">
-        <v>0.02183908045977011</v>
+        <v>0.167741935483871</v>
       </c>
       <c r="W4">
-        <v>-0.05108910891089109</v>
+        <v>-0.01127049180327869</v>
       </c>
       <c r="X4">
-        <v>0.06525148893604783</v>
+        <v>0.1225042463868321</v>
       </c>
       <c r="Y4">
-        <v>-0.1163405978469389</v>
+        <v>-0.1337747381901108</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.04926584234930449</v>
+        <v>-0.03852459016393443</v>
       </c>
       <c r="AB4">
-        <v>0.06343138329530354</v>
+        <v>0.1182033976823925</v>
       </c>
       <c r="AC4">
-        <v>-0.112697225644608</v>
+        <v>-0.1567279878463269</v>
       </c>
       <c r="AD4">
-        <v>0.194</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.194</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AG4">
-        <v>0.118</v>
+        <v>-0.7370000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.05280348394120849</v>
+        <v>0.06772524960904606</v>
       </c>
       <c r="AI4">
-        <v>0.01644904188570459</v>
+        <v>0.0242015217297855</v>
       </c>
       <c r="AJ4">
-        <v>0.03279599777654253</v>
+        <v>-0.1050905461286183</v>
       </c>
       <c r="AK4">
-        <v>0.0100699778119133</v>
+        <v>-0.03355643582388563</v>
       </c>
       <c r="AL4">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="AM4">
-        <v>0.013</v>
+        <v>0.011</v>
+      </c>
+      <c r="AN4">
+        <v>-0.6325842696629213</v>
       </c>
       <c r="AO4">
-        <v>-39.23076923076923</v>
+        <v>-81.18181818181819</v>
+      </c>
+      <c r="AP4">
+        <v>0.8280898876404496</v>
       </c>
       <c r="AQ4">
-        <v>-39.23076923076923</v>
+        <v>-81.18181818181819</v>
       </c>
     </row>
     <row r="5">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-0.652</v>
+        <v>-0.898</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -936,31 +936,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.228</v>
+        <v>0.192</v>
       </c>
       <c r="V5">
-        <v>0.01884297520661157</v>
+        <v>0.02082429501084599</v>
       </c>
       <c r="W5">
-        <v>-0.06841552990556139</v>
+        <v>-0.08238532110091742</v>
       </c>
       <c r="X5">
-        <v>0.06291894143364518</v>
+        <v>0.117501616232444</v>
       </c>
       <c r="Y5">
-        <v>-0.1313344713392066</v>
+        <v>-0.1998869373333615</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.06857383256205302</v>
+        <v>-0.08414542728635682</v>
       </c>
       <c r="AB5">
-        <v>0.06291894143364518</v>
+        <v>0.117501616232444</v>
       </c>
       <c r="AC5">
-        <v>-0.1314927739956982</v>
+        <v>-0.2016470435188009</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.228</v>
+        <v>-0.192</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.01920485175202157</v>
+        <v>-0.02126716880815241</v>
       </c>
       <c r="AK5">
-        <v>-0.02136431784107946</v>
+        <v>-0.02049530315969257</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>-0</v>
       </c>
       <c r="AP5">
-        <v>0.4108108108108108</v>
+        <v>0.3248730964467005</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ireland/ireland_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_precious_metals.xlsx
@@ -587,8 +587,23 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="G2">
+        <v>-70.21052631578948</v>
+      </c>
+      <c r="H2">
+        <v>-70.21052631578948</v>
+      </c>
+      <c r="I2">
+        <v>-296.9473684210526</v>
+      </c>
+      <c r="J2">
+        <v>-296.9473684210526</v>
+      </c>
       <c r="K2">
-        <v>-1.158</v>
+        <v>-5.377</v>
+      </c>
+      <c r="L2">
+        <v>-283</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.619</v>
+        <v>0.972</v>
       </c>
       <c r="V2">
-        <v>0.08512092534174553</v>
+        <v>0.05988909426987061</v>
       </c>
       <c r="W2">
-        <v>-0.01127049180327869</v>
+        <v>-0.0303921568627451</v>
       </c>
       <c r="X2">
-        <v>0.1225042463868321</v>
+        <v>0.09648622217111555</v>
       </c>
       <c r="Y2">
-        <v>-0.1337747381901108</v>
+        <v>-0.1268783790338606</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.0004740164159369308</v>
       </c>
       <c r="AA2">
-        <v>-0.03852459016393443</v>
+        <v>-0.03152030494062455</v>
       </c>
       <c r="AB2">
-        <v>0.1180667377260628</v>
+        <v>0.09557994455274114</v>
       </c>
       <c r="AC2">
-        <v>-0.1567279878463269</v>
+        <v>-0.1271002494933657</v>
       </c>
       <c r="AD2">
-        <v>0.742</v>
+        <v>0.295</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.742</v>
+        <v>0.295</v>
       </c>
       <c r="AG2">
-        <v>-0.877</v>
+        <v>-0.6769999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.03754680700333974</v>
+        <v>0.0178517397881997</v>
       </c>
       <c r="AI2">
-        <v>0.01717513078098236</v>
+        <v>0.006930576764947727</v>
       </c>
       <c r="AJ2">
-        <v>-0.04833820206140109</v>
+        <v>-0.04352857969523564</v>
       </c>
       <c r="AK2">
-        <v>-0.02109034942163865</v>
+        <v>-0.01627677734234126</v>
       </c>
       <c r="AL2">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AM2">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AN2">
-        <v>-0.5010128291694801</v>
+        <v>-0.2211394302848576</v>
       </c>
       <c r="AO2">
-        <v>-115.1052631578948</v>
+        <v>-282.1</v>
       </c>
       <c r="AP2">
-        <v>0.5921674544226875</v>
+        <v>0.5074962518740629</v>
       </c>
       <c r="AQ2">
-        <v>-115.1052631578948</v>
+        <v>-282.1</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +713,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>0.015</v>
+        <v>-0.31</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -707,7 +722,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -716,73 +731,73 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
+        <v>0.124</v>
+      </c>
+      <c r="V3">
+        <v>0.04381625441696113</v>
+      </c>
+      <c r="W3">
+        <v>-0.0303921568627451</v>
+      </c>
+      <c r="X3">
+        <v>0.0977214748836308</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1281136317463759</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>-0.03092079594225517</v>
+      </c>
+      <c r="AB3">
+        <v>0.09578130050725792</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1267020964495131</v>
+      </c>
+      <c r="AD3">
         <v>0.127</v>
       </c>
-      <c r="V3">
-        <v>0.06195121951219513</v>
-      </c>
-      <c r="W3">
-        <v>0.001293103448275862</v>
-      </c>
-      <c r="X3">
-        <v>0.1235146116677643</v>
-      </c>
-      <c r="Y3">
-        <v>-0.1222215082194884</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>-0.03379416282642089</v>
-      </c>
-      <c r="AB3">
-        <v>0.1180667377260628</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1518609005524836</v>
-      </c>
-      <c r="AD3">
-        <v>0.179</v>
-      </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.179</v>
+        <v>0.127</v>
       </c>
       <c r="AG3">
-        <v>0.05199999999999999</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="AH3">
-        <v>0.08030506953790939</v>
+        <v>0.04294893473114644</v>
       </c>
       <c r="AI3">
-        <v>0.01724636284805858</v>
+        <v>0.01206421582597131</v>
       </c>
       <c r="AJ3">
-        <v>0.0247383444338725</v>
+        <v>0.001058948111542535</v>
       </c>
       <c r="AK3">
-        <v>0.005072181037846273</v>
+        <v>0.0002883783523983469</v>
       </c>
       <c r="AL3">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="AM3">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="AO3">
-        <v>-49.5</v>
+        <v>-79.25</v>
       </c>
       <c r="AQ3">
-        <v>-49.5</v>
+        <v>-79.25</v>
       </c>
     </row>
     <row r="4">
@@ -802,7 +817,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-0.275</v>
+        <v>-0.387</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -826,73 +841,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.3</v>
+        <v>0.595</v>
       </c>
       <c r="V4">
-        <v>0.167741935483871</v>
+        <v>0.07074910820451842</v>
       </c>
       <c r="W4">
-        <v>-0.01127049180327869</v>
+        <v>-0.01825471698113208</v>
       </c>
       <c r="X4">
-        <v>0.1225042463868321</v>
+        <v>0.09648622217111555</v>
       </c>
       <c r="Y4">
-        <v>-0.1337747381901108</v>
+        <v>-0.1147409391522476</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.03852459016393443</v>
+        <v>-0.03152030494062455</v>
       </c>
       <c r="AB4">
-        <v>0.1182033976823925</v>
+        <v>0.09557994455274114</v>
       </c>
       <c r="AC4">
-        <v>-0.1567279878463269</v>
+        <v>-0.1271002494933657</v>
       </c>
       <c r="AD4">
-        <v>0.5629999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.5629999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="AG4">
-        <v>-0.7370000000000001</v>
+        <v>-0.4269999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.06772524960904606</v>
+        <v>0.01958498484495221</v>
       </c>
       <c r="AI4">
-        <v>0.0242015217297855</v>
+        <v>0.006648725660914991</v>
       </c>
       <c r="AJ4">
-        <v>-0.1050905461286183</v>
+        <v>-0.05348866340974569</v>
       </c>
       <c r="AK4">
-        <v>-0.03355643582388563</v>
+        <v>-0.01730636728407571</v>
       </c>
       <c r="AL4">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AM4">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AN4">
-        <v>-0.6325842696629213</v>
+        <v>-0.268370607028754</v>
       </c>
       <c r="AO4">
-        <v>-81.18181818181819</v>
+        <v>-40.3125</v>
       </c>
       <c r="AP4">
-        <v>0.8280898876404496</v>
+        <v>0.682108626198083</v>
       </c>
       <c r="AQ4">
-        <v>-81.18181818181819</v>
+        <v>-40.3125</v>
       </c>
     </row>
     <row r="5">
@@ -911,8 +926,23 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="G5">
+        <v>-37.26315789473684</v>
+      </c>
+      <c r="H5">
+        <v>-37.26315789473684</v>
+      </c>
+      <c r="I5">
+        <v>-246.3157894736842</v>
+      </c>
+      <c r="J5">
+        <v>-246.3157894736842</v>
+      </c>
       <c r="K5">
-        <v>-0.898</v>
+        <v>-4.68</v>
+      </c>
+      <c r="L5">
+        <v>-246.3157894736842</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -936,31 +966,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.192</v>
+        <v>0.253</v>
       </c>
       <c r="V5">
-        <v>0.02082429501084599</v>
+        <v>0.05070140280561122</v>
       </c>
       <c r="W5">
-        <v>-0.08238532110091742</v>
+        <v>-0.4895397489539748</v>
       </c>
       <c r="X5">
-        <v>0.117501616232444</v>
+        <v>0.09549523529964729</v>
       </c>
       <c r="Y5">
-        <v>-0.1998869373333615</v>
+        <v>-0.5850349842536221</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.002028181041844577</v>
       </c>
       <c r="AA5">
-        <v>-0.08414542728635682</v>
+        <v>-0.4995730145175064</v>
       </c>
       <c r="AB5">
-        <v>0.117501616232444</v>
+        <v>0.09549523529964729</v>
       </c>
       <c r="AC5">
-        <v>-0.2016470435188009</v>
+        <v>-0.5950682498171537</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -972,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.192</v>
+        <v>-0.253</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -981,10 +1011,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.02126716880815241</v>
+        <v>-0.05340933080008444</v>
       </c>
       <c r="AK5">
-        <v>-0.02049530315969257</v>
+        <v>-0.03882154365505601</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -996,7 +1026,7 @@
         <v>-0</v>
       </c>
       <c r="AP5">
-        <v>0.3248730964467005</v>
+        <v>0.3573446327683616</v>
       </c>
     </row>
   </sheetData>
